--- a/Aug_2026/Daily Sales/04-08-26/Raheem.xlsx
+++ b/Aug_2026/Daily Sales/04-08-26/Raheem.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{610AB752-9D34-4BC0-BC21-BB86AD6E150E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51E190CE-CEA9-488C-BD21-26ABC7505D98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="594" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3978" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3948" uniqueCount="517">
   <si>
     <t>Sr.No</t>
   </si>
@@ -2664,7 +2664,7 @@
     <xf numFmtId="43" fontId="32" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="30" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="412">
+  <cellXfs count="413">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3843,6 +3843,9 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="18" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -7439,8 +7442,8 @@
         <v>41</v>
       </c>
       <c r="I15" s="362"/>
-      <c r="J15" s="143" t="s">
-        <v>59</v>
+      <c r="J15" s="412">
+        <v>0.14000000000000001</v>
       </c>
       <c r="K15" s="144" t="s">
         <v>39</v>
@@ -8861,8 +8864,8 @@
         <v>41</v>
       </c>
       <c r="I15" s="362"/>
-      <c r="J15" s="143" t="s">
-        <v>59</v>
+      <c r="J15" s="412">
+        <v>0.14000000000000001</v>
       </c>
       <c r="K15" s="144" t="s">
         <v>39</v>
@@ -10283,8 +10286,8 @@
         <v>41</v>
       </c>
       <c r="I15" s="362"/>
-      <c r="J15" s="143" t="s">
-        <v>59</v>
+      <c r="J15" s="412">
+        <v>0.14000000000000001</v>
       </c>
       <c r="K15" s="144" t="s">
         <v>39</v>
@@ -11705,8 +11708,8 @@
         <v>41</v>
       </c>
       <c r="I15" s="362"/>
-      <c r="J15" s="143" t="s">
-        <v>59</v>
+      <c r="J15" s="412">
+        <v>0.14000000000000001</v>
       </c>
       <c r="K15" s="144" t="s">
         <v>39</v>
@@ -13127,8 +13130,8 @@
         <v>41</v>
       </c>
       <c r="I15" s="362"/>
-      <c r="J15" s="143" t="s">
-        <v>59</v>
+      <c r="J15" s="412">
+        <v>0.14000000000000001</v>
       </c>
       <c r="K15" s="144" t="s">
         <v>39</v>
@@ -14549,8 +14552,8 @@
         <v>41</v>
       </c>
       <c r="I15" s="362"/>
-      <c r="J15" s="143" t="s">
-        <v>59</v>
+      <c r="J15" s="412">
+        <v>0.14000000000000001</v>
       </c>
       <c r="K15" s="144" t="s">
         <v>39</v>
@@ -15971,8 +15974,8 @@
         <v>41</v>
       </c>
       <c r="I15" s="362"/>
-      <c r="J15" s="143" t="s">
-        <v>59</v>
+      <c r="J15" s="412">
+        <v>0.14000000000000001</v>
       </c>
       <c r="K15" s="144" t="s">
         <v>39</v>
@@ -17393,8 +17396,8 @@
         <v>41</v>
       </c>
       <c r="I15" s="362"/>
-      <c r="J15" s="143" t="s">
-        <v>59</v>
+      <c r="J15" s="412">
+        <v>0.14000000000000001</v>
       </c>
       <c r="K15" s="144" t="s">
         <v>39</v>
@@ -18815,8 +18818,8 @@
         <v>41</v>
       </c>
       <c r="I15" s="362"/>
-      <c r="J15" s="143" t="s">
-        <v>59</v>
+      <c r="J15" s="412">
+        <v>0.14000000000000001</v>
       </c>
       <c r="K15" s="144" t="s">
         <v>39</v>
@@ -20237,8 +20240,8 @@
         <v>41</v>
       </c>
       <c r="I15" s="362"/>
-      <c r="J15" s="143" t="s">
-        <v>59</v>
+      <c r="J15" s="412">
+        <v>0.14000000000000001</v>
       </c>
       <c r="K15" s="144" t="s">
         <v>39</v>
@@ -24074,8 +24077,8 @@
         <v>41</v>
       </c>
       <c r="I15" s="362"/>
-      <c r="J15" s="143" t="s">
-        <v>59</v>
+      <c r="J15" s="412">
+        <v>0.14000000000000001</v>
       </c>
       <c r="K15" s="144" t="s">
         <v>39</v>
@@ -25496,8 +25499,8 @@
         <v>41</v>
       </c>
       <c r="I15" s="362"/>
-      <c r="J15" s="143" t="s">
-        <v>59</v>
+      <c r="J15" s="412">
+        <v>0.14000000000000001</v>
       </c>
       <c r="K15" s="144" t="s">
         <v>39</v>
@@ -26918,8 +26921,8 @@
         <v>41</v>
       </c>
       <c r="I15" s="362"/>
-      <c r="J15" s="143" t="s">
-        <v>59</v>
+      <c r="J15" s="412">
+        <v>0.14000000000000001</v>
       </c>
       <c r="K15" s="144" t="s">
         <v>39</v>
@@ -28340,8 +28343,8 @@
         <v>41</v>
       </c>
       <c r="I15" s="362"/>
-      <c r="J15" s="143" t="s">
-        <v>59</v>
+      <c r="J15" s="412">
+        <v>0.14000000000000001</v>
       </c>
       <c r="K15" s="144" t="s">
         <v>39</v>
@@ -29762,8 +29765,8 @@
         <v>41</v>
       </c>
       <c r="I15" s="362"/>
-      <c r="J15" s="143" t="s">
-        <v>59</v>
+      <c r="J15" s="412">
+        <v>0.14000000000000001</v>
       </c>
       <c r="K15" s="144" t="s">
         <v>39</v>
@@ -31184,8 +31187,8 @@
         <v>41</v>
       </c>
       <c r="I15" s="362"/>
-      <c r="J15" s="143" t="s">
-        <v>59</v>
+      <c r="J15" s="412">
+        <v>0.14000000000000001</v>
       </c>
       <c r="K15" s="144" t="s">
         <v>39</v>
@@ -32606,8 +32609,8 @@
         <v>41</v>
       </c>
       <c r="I15" s="362"/>
-      <c r="J15" s="143" t="s">
-        <v>59</v>
+      <c r="J15" s="412">
+        <v>0.14000000000000001</v>
       </c>
       <c r="K15" s="144" t="s">
         <v>39</v>
@@ -34028,8 +34031,8 @@
         <v>41</v>
       </c>
       <c r="I15" s="362"/>
-      <c r="J15" s="143" t="s">
-        <v>59</v>
+      <c r="J15" s="412">
+        <v>0.14000000000000001</v>
       </c>
       <c r="K15" s="144" t="s">
         <v>39</v>
@@ -35450,8 +35453,8 @@
         <v>41</v>
       </c>
       <c r="I15" s="362"/>
-      <c r="J15" s="143" t="s">
-        <v>59</v>
+      <c r="J15" s="412">
+        <v>0.14000000000000001</v>
       </c>
       <c r="K15" s="144" t="s">
         <v>39</v>
@@ -36872,8 +36875,8 @@
         <v>41</v>
       </c>
       <c r="I15" s="362"/>
-      <c r="J15" s="143" t="s">
-        <v>59</v>
+      <c r="J15" s="412">
+        <v>0.14000000000000001</v>
       </c>
       <c r="K15" s="144" t="s">
         <v>39</v>
@@ -41067,8 +41070,8 @@
         <v>41</v>
       </c>
       <c r="I15" s="362"/>
-      <c r="J15" s="143" t="s">
-        <v>59</v>
+      <c r="J15" s="412">
+        <v>0.14000000000000001</v>
       </c>
       <c r="K15" s="144" t="s">
         <v>39</v>
@@ -42489,8 +42492,8 @@
         <v>41</v>
       </c>
       <c r="I15" s="362"/>
-      <c r="J15" s="143" t="s">
-        <v>59</v>
+      <c r="J15" s="412">
+        <v>0.14000000000000001</v>
       </c>
       <c r="K15" s="144" t="s">
         <v>39</v>
@@ -43911,8 +43914,8 @@
         <v>41</v>
       </c>
       <c r="I15" s="362"/>
-      <c r="J15" s="143" t="s">
-        <v>59</v>
+      <c r="J15" s="412">
+        <v>0.14000000000000001</v>
       </c>
       <c r="K15" s="144" t="s">
         <v>39</v>
@@ -45333,8 +45336,8 @@
         <v>41</v>
       </c>
       <c r="I15" s="362"/>
-      <c r="J15" s="143" t="s">
-        <v>59</v>
+      <c r="J15" s="412">
+        <v>0.14000000000000001</v>
       </c>
       <c r="K15" s="144" t="s">
         <v>39</v>
@@ -46755,8 +46758,8 @@
         <v>41</v>
       </c>
       <c r="I15" s="362"/>
-      <c r="J15" s="143" t="s">
-        <v>59</v>
+      <c r="J15" s="412">
+        <v>0.14000000000000001</v>
       </c>
       <c r="K15" s="144" t="s">
         <v>39</v>
@@ -47882,7 +47885,7 @@
       <c r="L4" s="368"/>
       <c r="M4" s="398">
         <f ca="1">TODAY()+1</f>
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="N4" s="398"/>
       <c r="O4" s="398"/>
@@ -47910,7 +47913,7 @@
       <c r="L5" s="368"/>
       <c r="M5" s="398">
         <f ca="1">M4-1</f>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="N5" s="367"/>
       <c r="O5" s="367"/>
@@ -54105,7 +54108,7 @@
       <c r="G3" s="358"/>
       <c r="H3" s="355">
         <f ca="1">TODAY()</f>
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="I3" s="355"/>
       <c r="J3" s="356"/>
@@ -55911,8 +55914,8 @@
         <v>41</v>
       </c>
       <c r="I15" s="362"/>
-      <c r="J15" s="143" t="s">
-        <v>59</v>
+      <c r="J15" s="412">
+        <v>0.14000000000000001</v>
       </c>
       <c r="K15" s="144" t="s">
         <v>39</v>
@@ -57346,8 +57349,8 @@
         <v>41</v>
       </c>
       <c r="I15" s="362"/>
-      <c r="J15" s="143" t="s">
-        <v>59</v>
+      <c r="J15" s="412">
+        <v>0.14000000000000001</v>
       </c>
       <c r="K15" s="144" t="s">
         <v>39</v>
@@ -58768,8 +58771,8 @@
         <v>41</v>
       </c>
       <c r="I15" s="362"/>
-      <c r="J15" s="143" t="s">
-        <v>59</v>
+      <c r="J15" s="412">
+        <v>0.14000000000000001</v>
       </c>
       <c r="K15" s="144" t="s">
         <v>39</v>
@@ -60190,8 +60193,8 @@
         <v>41</v>
       </c>
       <c r="I15" s="362"/>
-      <c r="J15" s="143" t="s">
-        <v>59</v>
+      <c r="J15" s="412">
+        <v>0.14000000000000001</v>
       </c>
       <c r="K15" s="144" t="s">
         <v>39</v>
@@ -61612,8 +61615,8 @@
         <v>41</v>
       </c>
       <c r="I15" s="362"/>
-      <c r="J15" s="143" t="s">
-        <v>59</v>
+      <c r="J15" s="412">
+        <v>0.14000000000000001</v>
       </c>
       <c r="K15" s="144" t="s">
         <v>39</v>
